--- a/artfynd/A 58277-2021 artfynd.xlsx
+++ b/artfynd/A 58277-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58277-2021 artfynd.xlsx
+++ b/artfynd/A 58277-2021 artfynd.xlsx
@@ -8411,7 +8411,7 @@
         <v>133130812</v>
       </c>
       <c r="B63" t="n">
-        <v>101357</v>
+        <v>101359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 58277-2021 artfynd.xlsx
+++ b/artfynd/A 58277-2021 artfynd.xlsx
@@ -8411,7 +8411,7 @@
         <v>133130812</v>
       </c>
       <c r="B63" t="n">
-        <v>101359</v>
+        <v>101367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 58277-2021 artfynd.xlsx
+++ b/artfynd/A 58277-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7142681</v>
+        <v>80845656</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1853</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fåssjödal, O om Närmovallokarna, Hls</t>
+          <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507647.24716666</v>
+        <v>507393</v>
       </c>
       <c r="R2" t="n">
-        <v>6895292.222219723</v>
+        <v>6895566</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-05-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,75 +756,74 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # lumpad gammal tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Hedvall</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Hedvall</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61608622</v>
+        <v>80845697</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1853</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fåssjödal / 1200 m NNV /, Hls</t>
+          <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507584.4666024556</v>
+        <v>507556</v>
       </c>
       <c r="R3" t="n">
-        <v>6895554.938142448</v>
+        <v>6895381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,27 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Detalj. 23 ex inom 6 m2.</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,31 +866,39 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>30-årig, lavrik sandtallskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal lumpad tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Wallén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61608623</v>
+        <v>504185</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,27 +925,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fåssjödal / 1200 m NNV /, Hls</t>
+          <t>Fåssjödal / 900 m NNV /, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507611.9594038491</v>
+        <v>507613</v>
       </c>
       <c r="R4" t="n">
-        <v>6895596.084366795</v>
+        <v>6895271</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,29 +967,24 @@
           <t>Ytterhogdal</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Z-Här-0650</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2005-05-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-05-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Detalj. 100 ex inom ca 15x25 m.</t>
+          <t>15 ex varav 1 bl. inom 3x7 m.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +999,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Z Län Floraväktarna</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1046,19 +1007,18 @@
           <t>Hanna Wallén</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61608621</v>
+        <v>61608622</v>
       </c>
       <c r="B5" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507600.87407211</v>
+        <v>507584</v>
       </c>
       <c r="R5" t="n">
-        <v>6895535.833390228</v>
+        <v>6895555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,24 +1092,14 @@
           <t>2005-05-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-05-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Detalj. 4 ex inom 20x20 cm.</t>
+          <t>Detalj. 23 ex inom 6 m2.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,15 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>71376931</v>
+        <v>7142681</v>
       </c>
       <c r="B6" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,33 +1156,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Närmovallokarna, Fåssjödal, Hls</t>
+          <t>Fåssjödal, O om Närmovallokarna, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507597.4087876587</v>
+        <v>507647</v>
       </c>
       <c r="R6" t="n">
-        <v>6895206.197803099</v>
+        <v>6895292</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,27 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1986-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Av 39 plantor var två i blom.Rel tät gallringsskog med mkt husmossa och lingon, en del ljung och enbuskar. Lokalen behöver glesas ut och brännas.</t>
+          <t>1986-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,27 +1222,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Olle Hedvall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Olle Hedvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57863965</v>
+        <v>61608621</v>
       </c>
       <c r="B7" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,27 +1264,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fåssjödal / 900 m NNV /, Hls</t>
+          <t>Fåssjödal / 1200 m NNV /, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507613.160658827</v>
+        <v>507601</v>
       </c>
       <c r="R7" t="n">
-        <v>6895271.134258922</v>
+        <v>6895536</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,34 +1306,19 @@
           <t>Ytterhogdal</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Z-Här-0650</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1994-05-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-05-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1994-05-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-05-24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Koordinat 6897589/1465729. (kopia in i floraväkteri)</t>
+          <t>Detalj. 4 ex inom 20x20 cm.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,71 +1338,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Hedvall</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Wallén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80122026</v>
+        <v>61608623</v>
       </c>
       <c r="B8" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2051</v>
+        <v>1853</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fåssjö, getryggen, Hls</t>
+          <t>Fåssjödal / 1200 m NNV /, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507592.6010781584</v>
+        <v>507612</v>
       </c>
       <c r="R8" t="n">
-        <v>6895472.31954608</v>
+        <v>6895596</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,27 +1419,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-09-25</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2005-05-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-09-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2005-05-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6 stora fruktkroppar I sandig sluttning längs "getrygg".</t>
+          <t>Detalj. 100 ex inom ca 15x25 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,19 +1438,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Hanna Wallén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1571,12 +1459,7 @@
         <v>80328825</v>
       </c>
       <c r="B9" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507591.9684585904</v>
+        <v>507592</v>
       </c>
       <c r="R9" t="n">
-        <v>6895545.617624774</v>
+        <v>6895546</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1698,59 +1581,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80845663</v>
+        <v>109724879</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fåssjödal, Hls</t>
+          <t>Fåssjödal, vägkant grusväg, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507237.1055927545</v>
+        <v>507740</v>
       </c>
       <c r="R10" t="n">
-        <v>6895540.16850226</v>
+        <v>6895305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,22 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,85 +1676,81 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>intill äldre tallar i ung sandtallskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Håkan Blomqvist, Bodil Carlsson, Tomas Rydkvist, SCA SCA</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80845632</v>
+        <v>133130812</v>
       </c>
       <c r="B11" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fåssjödal, Hls</t>
+          <t>Närmovallokarna, Närmovallokarna, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507498.0321046506</v>
+        <v>507611</v>
       </c>
       <c r="R11" t="n">
-        <v>6895736.818982505</v>
+        <v>6895283</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1903,22 +1774,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11 plantor varav 6 i blom på nybränd yta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,58 +1805,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>30-årig sandtallskog uppe på ås</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80845672</v>
+        <v>80845647</v>
       </c>
       <c r="B12" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1999,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507561.2224317749</v>
+        <v>507438</v>
       </c>
       <c r="R12" t="n">
-        <v>6895286.892245724</v>
+        <v>6895632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,21 +1898,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +1914,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>30-årig, lavrik, tät sandtallskog på åskrön</t>
+          <t>30-årig, sandtallskog av stavatyp</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2076,37 +1932,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80845686</v>
+        <v>80845653</v>
       </c>
       <c r="B13" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2125,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507571.1791343682</v>
+        <v>507436</v>
       </c>
       <c r="R13" t="n">
-        <v>6895433.986925049</v>
+        <v>6895570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,21 +2009,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2184,7 +2025,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>30-årig tallskog i sydsluttning av ås</t>
+          <t>30-årig, lavrik sandtallskog i västsluttning</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2202,37 +2043,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80845681</v>
+        <v>80845682</v>
       </c>
       <c r="B14" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2251,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507625.1311384683</v>
+        <v>507616</v>
       </c>
       <c r="R14" t="n">
-        <v>6895353.803133479</v>
+        <v>6895365</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2284,21 +2120,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2311,6 +2137,11 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>35-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>renlav, väggmossa</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2328,15 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80845658</v>
+        <v>80845695</v>
       </c>
       <c r="B15" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2344,43 +2170,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507411.7767594712</v>
+        <v>507507</v>
       </c>
       <c r="R15" t="n">
-        <v>6895628.785500179</v>
+        <v>6895473</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2410,21 +2227,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2436,12 +2243,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
-        </is>
+          <t>30-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>stigkant</t>
+          <t>1 substratenheter # murken gammal tallstock</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2459,62 +2269,55 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80845639</v>
+        <v>80122026</v>
       </c>
       <c r="B16" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>2051</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fåssjödal, Hls</t>
+          <t>Fåssjö, getryggen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507519.9600621722</v>
+        <v>507593</v>
       </c>
       <c r="R16" t="n">
-        <v>6895547.790596373</v>
+        <v>6895472</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2538,22 +2341,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2019-09-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2019-09-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6 stora fruktkroppar I sandig sluttning längs "getrygg".</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2562,60 +2370,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>30-årig sandtallskog uppe på ås</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80845654</v>
+        <v>80845689</v>
       </c>
       <c r="B17" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>2051</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2634,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507436.2186701301</v>
+        <v>507549</v>
       </c>
       <c r="R17" t="n">
-        <v>6895570.014557563</v>
+        <v>6895421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2667,21 +2466,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2693,7 +2482,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
+          <t>30-årig tallskog på åskam</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>lav, lingon, väggmossa</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2711,19 +2505,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80845701</v>
+        <v>80845644</v>
       </c>
       <c r="B18" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2760,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507597.8736837957</v>
+        <v>507533</v>
       </c>
       <c r="R18" t="n">
-        <v>6895414.904588047</v>
+        <v>6895686</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2793,21 +2582,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2819,7 +2598,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
+          <t>30-årig, sandtallskog av stavatyp</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2837,37 +2616,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80845649</v>
+        <v>80845701</v>
       </c>
       <c r="B19" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2886,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507475.8744758337</v>
+        <v>507598</v>
       </c>
       <c r="R19" t="n">
-        <v>6895608.852020938</v>
+        <v>6895415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2919,21 +2693,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2945,7 +2709,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>30-årig, lavrik sandtallskog i västsluttning</t>
+          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2963,37 +2727,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>80845676</v>
+        <v>80845628</v>
       </c>
       <c r="B20" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3012,10 +2771,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507644.0015690695</v>
+        <v>507657</v>
       </c>
       <c r="R20" t="n">
-        <v>6895280.075288182</v>
+        <v>6895740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3045,21 +2804,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3071,7 +2820,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>35-årig, tät sandtallskog</t>
+          <t>30-årig tallskog på åskrön</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>sandväg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3089,37 +2843,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80845625</v>
+        <v>80845632</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3138,10 +2887,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507721.1200480817</v>
+        <v>507498</v>
       </c>
       <c r="R21" t="n">
-        <v>6895499.223521954</v>
+        <v>6895737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3171,21 +2920,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3197,7 +2936,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>ung sandtallskog</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3215,37 +2954,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>80845623</v>
+        <v>80845642</v>
       </c>
       <c r="B22" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3264,10 +2998,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507733.9808366721</v>
+        <v>507528</v>
       </c>
       <c r="R22" t="n">
-        <v>6895396.071550217</v>
+        <v>6895623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3297,21 +3031,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3323,7 +3047,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>ung sandtallskog</t>
+          <t>30-årig, sandtallskog av stavatyp</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3341,37 +3065,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>80845690</v>
+        <v>80845657</v>
       </c>
       <c r="B23" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3390,10 +3109,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507549.9660383568</v>
+        <v>507390</v>
       </c>
       <c r="R23" t="n">
-        <v>6895510.974693103</v>
+        <v>6895562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3423,21 +3142,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3449,7 +3158,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>30-årig, tät sandtallskog</t>
+          <t>30-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3467,37 +3176,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80845702</v>
+        <v>80845660</v>
       </c>
       <c r="B24" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3516,10 +3220,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507597.8736837957</v>
+        <v>507303</v>
       </c>
       <c r="R24" t="n">
-        <v>6895414.904588047</v>
+        <v>6895505</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3549,21 +3253,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3575,12 +3269,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>renlav, islandslav</t>
+          <t>30-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3598,37 +3287,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>80845696</v>
+        <v>80845662</v>
       </c>
       <c r="B25" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3647,10 +3331,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507490.218188537</v>
+        <v>507299</v>
       </c>
       <c r="R25" t="n">
-        <v>6895466.021083238</v>
+        <v>6895598</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3680,21 +3364,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3706,12 +3380,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>30-årig, tät sandtallskog</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>liten stig</t>
+          <t>30-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3729,37 +3398,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80845704</v>
+        <v>80845624</v>
       </c>
       <c r="B26" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3778,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507586.0846049134</v>
+        <v>507705</v>
       </c>
       <c r="R26" t="n">
-        <v>6895459.232187851</v>
+        <v>6895464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3811,21 +3475,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3837,7 +3491,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>40-årig sandtallskog på ås</t>
+          <t>ung sandtallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3855,37 +3509,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>80845655</v>
+        <v>80845631</v>
       </c>
       <c r="B27" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3904,10 +3553,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507403.9198003762</v>
+        <v>507562</v>
       </c>
       <c r="R27" t="n">
-        <v>6895587.217517074</v>
+        <v>6895749</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3937,21 +3586,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3963,7 +3602,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
+          <t>30-årig sandtallskog uppe på ås</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>sandvägskant</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3981,37 +3625,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>80845674</v>
+        <v>80845658</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4030,10 +3669,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507668.8656070646</v>
+        <v>507412</v>
       </c>
       <c r="R28" t="n">
-        <v>6895244.179681323</v>
+        <v>6895629</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4063,21 +3702,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4089,7 +3718,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>35-årig, tät sandtallskog</t>
+          <t>30-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4107,37 +3741,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>80845635</v>
+        <v>80845672</v>
       </c>
       <c r="B29" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4156,10 +3785,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507628.0006850036</v>
+        <v>507561</v>
       </c>
       <c r="R29" t="n">
-        <v>6895532.159676078</v>
+        <v>6895287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4189,21 +3818,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4215,7 +3834,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
+          <t>30-årig, lavrik, tät sandtallskog på åskrön</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4233,37 +3852,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>80845633</v>
+        <v>80845675</v>
       </c>
       <c r="B30" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4282,10 +3896,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507641.0901099125</v>
+        <v>507653</v>
       </c>
       <c r="R30" t="n">
-        <v>6895533.123061468</v>
+        <v>6895271</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4315,21 +3929,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4341,7 +3945,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
+          <t>35-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4359,15 +3963,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>80845628</v>
+        <v>80845623</v>
       </c>
       <c r="B31" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4375,21 +3974,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4408,10 +4007,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507656.9847969954</v>
+        <v>507734</v>
       </c>
       <c r="R31" t="n">
-        <v>6895739.97732513</v>
+        <v>6895396</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,21 +4040,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4467,12 +4056,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>30-årig tallskog på åskrön</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>sandväg</t>
+          <t>ung sandtallskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4490,37 +4074,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>80845692</v>
+        <v>80845625</v>
       </c>
       <c r="B32" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4539,10 +4118,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507519.1030470812</v>
+        <v>507721</v>
       </c>
       <c r="R32" t="n">
-        <v>6895512.773223223</v>
+        <v>6895499</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4572,21 +4151,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4598,7 +4167,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>30-årig, tät sandtallskog</t>
+          <t>ung sandtallskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4616,37 +4185,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>80845653</v>
+        <v>80845633</v>
       </c>
       <c r="B33" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4665,10 +4229,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507436.2186701301</v>
+        <v>507641</v>
       </c>
       <c r="R33" t="n">
-        <v>6895570.014557563</v>
+        <v>6895533</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4698,21 +4262,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4724,7 +4278,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>30-årig, lavrik sandtallskog i västsluttning</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4742,37 +4296,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>80845626</v>
+        <v>80845634</v>
       </c>
       <c r="B34" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4791,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507737.9554087849</v>
+        <v>507616</v>
       </c>
       <c r="R34" t="n">
-        <v>6895497.861486414</v>
+        <v>6895520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4824,21 +4373,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4850,7 +4389,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>30-årig tallskog på åskrön</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4868,15 +4407,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>80845695</v>
+        <v>80845636</v>
       </c>
       <c r="B35" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4884,34 +4418,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507507.0349066497</v>
+        <v>507628</v>
       </c>
       <c r="R35" t="n">
-        <v>6895473.061702783</v>
+        <v>6895549</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4941,21 +4484,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4967,15 +4500,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>30-årig, tät sandtallskog</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>1 substratenheter # murken gammal tallstock</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4993,15 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80845656</v>
+        <v>80845637</v>
       </c>
       <c r="B36" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5009,34 +4529,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507393.2122806345</v>
+        <v>507552</v>
       </c>
       <c r="R36" t="n">
-        <v>6895566.185034747</v>
+        <v>6895601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5066,21 +4595,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5092,15 +4611,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>1 substratenheter # lumpad gammal tallåga</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5118,15 +4629,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>80845644</v>
+        <v>80845645</v>
       </c>
       <c r="B37" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,21 +4640,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5167,10 +4673,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507533.2103090777</v>
+        <v>507495</v>
       </c>
       <c r="R37" t="n">
-        <v>6895686.010994514</v>
+        <v>6895711</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5200,19 +4706,9 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5244,19 +4740,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>80845699</v>
+        <v>80845648</v>
       </c>
       <c r="B38" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5293,10 +4784,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507620.8543263394</v>
+        <v>507439</v>
       </c>
       <c r="R38" t="n">
-        <v>6895384.141650057</v>
+        <v>6895618</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5326,21 +4817,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5352,7 +4833,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
+          <t>30-årig, lavrik sandtallskog i västsluttning</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5370,15 +4851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>80845688</v>
+        <v>80845663</v>
       </c>
       <c r="B39" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5386,21 +4862,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5419,10 +4895,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507549.2326781562</v>
+        <v>507237</v>
       </c>
       <c r="R39" t="n">
-        <v>6895420.864876978</v>
+        <v>6895540</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5452,21 +4928,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5478,7 +4944,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>30-årig tallskog på åskam</t>
+          <t>intill äldre tallar i ung sandtallskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5496,19 +4962,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>80845637</v>
+        <v>80845673</v>
       </c>
       <c r="B40" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5545,10 +5006,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507552.1019888776</v>
+        <v>507635</v>
       </c>
       <c r="R40" t="n">
-        <v>6895601.085249974</v>
+        <v>6895322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5578,21 +5039,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5604,7 +5055,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
+          <t>35-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5622,15 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>80845660</v>
+        <v>80845674</v>
       </c>
       <c r="B41" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5638,21 +5084,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5671,10 +5117,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507303.1075499479</v>
+        <v>507669</v>
       </c>
       <c r="R41" t="n">
-        <v>6895504.82842172</v>
+        <v>6895244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5704,21 +5150,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5730,7 +5166,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
+          <t>35-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5748,37 +5184,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>80845698</v>
+        <v>80845676</v>
       </c>
       <c r="B42" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5797,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507551.1677896366</v>
+        <v>507644</v>
       </c>
       <c r="R42" t="n">
-        <v>6895391.922033429</v>
+        <v>6895280</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5830,21 +5261,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5856,7 +5277,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>30-årig lavrik sandtallskog i sydsluttning av dödisgrop</t>
+          <t>35-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5874,15 +5295,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>80845624</v>
+        <v>80845680</v>
       </c>
       <c r="B43" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5890,21 +5306,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5923,10 +5339,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507704.8354806738</v>
+        <v>507603</v>
       </c>
       <c r="R43" t="n">
-        <v>6895464.170293237</v>
+        <v>6895326</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5956,21 +5372,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5982,7 +5388,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>ung sandtallskog</t>
+          <t>35-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6000,37 +5406,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80845694</v>
+        <v>80845699</v>
       </c>
       <c r="B44" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6049,10 +5450,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507528.977015655</v>
+        <v>507621</v>
       </c>
       <c r="R44" t="n">
-        <v>6895488.05077998</v>
+        <v>6895384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6082,21 +5483,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6108,7 +5499,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>30-årig, tät sandtallskog</t>
+          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6126,19 +5517,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>80845636</v>
+        <v>80845705</v>
       </c>
       <c r="B45" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -6175,10 +5561,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507627.9626584956</v>
+        <v>507651</v>
       </c>
       <c r="R45" t="n">
-        <v>6895548.966963329</v>
+        <v>6895325</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6208,21 +5594,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6234,7 +5610,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
+          <t>40-årig sandtallskog på ås</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6252,19 +5628,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>80845643</v>
+        <v>80845635</v>
       </c>
       <c r="B46" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -6301,10 +5672,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507528.0966275693</v>
+        <v>507628</v>
       </c>
       <c r="R46" t="n">
-        <v>6895672.927709308</v>
+        <v>6895532</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6334,21 +5705,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6360,7 +5721,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>30-årig, sandtallskog av stavatyp</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6378,37 +5739,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>80845682</v>
+        <v>80845639</v>
       </c>
       <c r="B47" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1958</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6427,10 +5783,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507616.2218111347</v>
+        <v>507520</v>
       </c>
       <c r="R47" t="n">
-        <v>6895364.988512523</v>
+        <v>6895548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6460,21 +5816,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6486,12 +5832,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>35-årig, tät sandtallskog</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>renlav, väggmossa</t>
+          <t>30-årig sandtallskog uppe på ås</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6509,15 +5850,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>80845631</v>
+        <v>80845643</v>
       </c>
       <c r="B48" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6525,21 +5861,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6558,10 +5894,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507562.0560277216</v>
+        <v>507528</v>
       </c>
       <c r="R48" t="n">
-        <v>6895749.099917985</v>
+        <v>6895673</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6591,21 +5927,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6617,12 +5943,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>sandvägskant</t>
+          <t>30-årig, sandtallskog av stavatyp</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6640,50 +5961,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>80845697</v>
+        <v>80845649</v>
       </c>
       <c r="B49" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507555.8675991453</v>
+        <v>507476</v>
       </c>
       <c r="R49" t="n">
-        <v>6895381.194030454</v>
+        <v>6895609</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6713,21 +6038,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6739,15 +6054,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>30-årig, lavrik sandtallskog</t>
-        </is>
-      </c>
-      <c r="AN49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal lumpad tallåga</t>
+          <t>30-årig, lavrik sandtallskog i västsluttning</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6765,37 +6072,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>80845689</v>
+        <v>80845654</v>
       </c>
       <c r="B50" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2051</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6814,10 +6116,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507549.2326781562</v>
+        <v>507436</v>
       </c>
       <c r="R50" t="n">
-        <v>6895420.864876978</v>
+        <v>6895570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6847,21 +6149,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6873,12 +6165,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>30-årig tallskog på åskam</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>lav, lingon, väggmossa</t>
+          <t>30-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6896,15 +6183,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80845642</v>
+        <v>80845655</v>
       </c>
       <c r="B51" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6912,21 +6194,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6945,10 +6227,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507528.2081726376</v>
+        <v>507404</v>
       </c>
       <c r="R51" t="n">
-        <v>6895622.974304052</v>
+        <v>6895587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6978,21 +6260,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7004,7 +6276,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>30-årig, sandtallskog av stavatyp</t>
+          <t>30-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7022,15 +6294,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>80845675</v>
+        <v>80845687</v>
       </c>
       <c r="B52" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7038,21 +6305,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7071,10 +6338,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507652.9059137279</v>
+        <v>507560</v>
       </c>
       <c r="R52" t="n">
-        <v>6895271.224232971</v>
+        <v>6895433</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7104,21 +6371,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7130,7 +6387,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>35-årig, tät sandtallskog</t>
+          <t>30-årig tallskog på åskam</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7148,19 +6405,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>80845687</v>
+        <v>80845698</v>
       </c>
       <c r="B53" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -7197,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507559.9595804383</v>
+        <v>507551</v>
       </c>
       <c r="R53" t="n">
-        <v>6895433.027977074</v>
+        <v>6895392</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,21 +6482,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7256,7 +6498,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>30-årig tallskog på åskam</t>
+          <t>30-årig lavrik sandtallskog i sydsluttning av dödisgrop</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7274,37 +6516,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>80845705</v>
+        <v>80845704</v>
       </c>
       <c r="B54" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7323,10 +6560,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>507650.9137115523</v>
+        <v>507586</v>
       </c>
       <c r="R54" t="n">
-        <v>6895324.913784339</v>
+        <v>6895459</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7356,19 +6593,9 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7400,15 +6627,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>80845662</v>
+        <v>80845629</v>
       </c>
       <c r="B55" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7416,21 +6638,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7449,10 +6671,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>507299.1649247966</v>
+        <v>507678</v>
       </c>
       <c r="R55" t="n">
-        <v>6895598.193831828</v>
+        <v>6895794</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7482,21 +6704,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7508,7 +6720,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
+          <t>30-årig tallskog på åskrön</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>stig med lav, lingon, väggmossa</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7526,37 +6743,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80845673</v>
+        <v>80845686</v>
       </c>
       <c r="B56" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7575,10 +6787,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>507635.0222063187</v>
+        <v>507571</v>
       </c>
       <c r="R56" t="n">
-        <v>6895322.07635335</v>
+        <v>6895434</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7608,21 +6820,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7634,7 +6836,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>35-årig, tät sandtallskog</t>
+          <t>30-årig tallskog i sydsluttning av ås</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7652,37 +6854,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80845645</v>
+        <v>80845688</v>
       </c>
       <c r="B57" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7701,10 +6898,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>507494.816500612</v>
+        <v>507549</v>
       </c>
       <c r="R57" t="n">
-        <v>6895711.135298693</v>
+        <v>6895421</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7734,21 +6931,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7760,7 +6947,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>30-årig, sandtallskog av stavatyp</t>
+          <t>30-årig tallskog på åskam</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7778,59 +6965,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>80845657</v>
+        <v>80845684</v>
       </c>
       <c r="B58" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>507389.9486384952</v>
+        <v>507488</v>
       </c>
       <c r="R58" t="n">
-        <v>6895561.976066922</v>
+        <v>6895374</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7860,21 +7033,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7886,7 +7049,15 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog</t>
+          <t>björkrik strandskog mot loke i dödisgrop</t>
+        </is>
+      </c>
+      <c r="AN58" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>50 substratenheter # vid basen av många enbuskar, bl.a en mkt gammal och hög</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7904,15 +7075,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>80845634</v>
+        <v>80845683</v>
       </c>
       <c r="B59" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7920,43 +7086,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>507615.871673793</v>
+        <v>507488</v>
       </c>
       <c r="R59" t="n">
-        <v>6895519.993545696</v>
+        <v>6895374</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7986,21 +7143,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -8012,7 +7159,15 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>30-årig sandtallskog uppe på ås</t>
+          <t>strandskog mot loke</t>
+        </is>
+      </c>
+      <c r="AN59" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>20 substratenheter # tidvis översvämmade enbuskar</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8030,37 +7185,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80845648</v>
+        <v>80845626</v>
       </c>
       <c r="B60" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -8079,10 +7229,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>507438.9178661078</v>
+        <v>507738</v>
       </c>
       <c r="R60" t="n">
-        <v>6895618.107500031</v>
+        <v>6895498</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8112,21 +7262,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -8138,7 +7278,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>30-årig, lavrik sandtallskog i västsluttning</t>
+          <t>30-årig tallskog på åskrön</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8156,37 +7296,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>80845680</v>
+        <v>80845681</v>
       </c>
       <c r="B61" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8205,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>507603.2170065035</v>
+        <v>507625</v>
       </c>
       <c r="R61" t="n">
-        <v>6895326.20659574</v>
+        <v>6895354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8238,19 +7373,9 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2019-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8282,37 +7407,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>80845647</v>
+        <v>80845690</v>
       </c>
       <c r="B62" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8331,10 +7451,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>507437.9518802936</v>
+        <v>507550</v>
       </c>
       <c r="R62" t="n">
-        <v>6895632.111158936</v>
+        <v>6895511</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8364,21 +7484,11 @@
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2019-10-08</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8390,7 +7500,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>30-årig, sandtallskog av stavatyp</t>
+          <t>30-årig, tät sandtallskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8408,62 +7518,57 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133130812</v>
+        <v>80845692</v>
       </c>
       <c r="B63" t="n">
-        <v>101367</v>
+        <v>91402</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1853</v>
+        <v>256703</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Närmovallokarna, Närmovallokarna, Hls</t>
+          <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>507611</v>
+        <v>507519</v>
       </c>
       <c r="R63" t="n">
-        <v>6895283</v>
+        <v>6895513</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8487,27 +7592,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>11 plantor varav 6 i blom på nybränd yta</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8518,19 +7608,367 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>30-årig, tät sandtallskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>80845694</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>507529</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6895488</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>30-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>80845696</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>507490</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6895466</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>30-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>liten stig</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>80845702</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>507598</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6895415</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>30-årig, tät, lavrik sandtallskog i västsluttning</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>renlav, islandslav</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58277-2021 artfynd.xlsx
+++ b/artfynd/A 58277-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845656</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/504185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61608622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7142681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61608621</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61608623</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80328825</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109724879</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1818,6 +1868,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133130812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,6 +1984,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845647</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845653</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2156,6 +2221,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845682</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2266,6 +2336,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845695</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2386,6 +2461,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80122026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845689</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845644</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845701</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2840,6 +2935,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845628</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2951,6 +3051,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845632</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3062,6 +3167,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845642</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3173,6 +3283,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845657</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3284,6 +3399,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845660</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3395,6 +3515,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845662</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3506,6 +3631,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845624</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3622,6 +3752,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845631</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3738,6 +3873,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845658</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3849,6 +3989,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845672</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3960,6 +4105,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845675</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4071,6 +4221,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845623</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4182,6 +4337,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845625</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4293,6 +4453,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845633</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4404,6 +4569,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845634</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4515,6 +4685,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845636</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4626,6 +4801,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845637</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4737,6 +4917,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845645</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4848,6 +5033,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845648</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4959,6 +5149,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845663</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5070,6 +5265,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845673</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5181,6 +5381,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845674</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5292,6 +5497,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845676</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5403,6 +5613,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845680</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5514,6 +5729,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845699</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5625,6 +5845,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845705</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5736,6 +5961,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845635</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5847,6 +6077,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845639</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5958,6 +6193,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845643</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6069,6 +6309,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845649</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6180,6 +6425,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845654</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6291,6 +6541,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845655</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6402,6 +6657,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845687</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6513,6 +6773,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845698</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6624,6 +6889,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845704</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6740,6 +7010,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845629</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6851,6 +7126,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845686</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6962,6 +7242,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845688</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7072,6 +7357,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845684</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7182,6 +7472,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845683</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7293,6 +7588,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845626</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7404,6 +7704,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845681</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7515,6 +7820,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845690</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7626,6 +7936,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845692</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7737,6 +8052,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845694</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7853,6 +8173,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845696</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7969,8 +8294,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>